--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129130282</v>
       </c>
       <c r="B2" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129131950</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129130282</v>
       </c>
       <c r="B2" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129131950</v>
+        <v>129130334</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>97555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537923</v>
+        <v>538004</v>
       </c>
       <c r="R3" t="n">
-        <v>6982809</v>
+        <v>6982735</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129130334</v>
+        <v>129131950</v>
       </c>
       <c r="B4" t="n">
-        <v>97553</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538004</v>
+        <v>537923</v>
       </c>
       <c r="R4" t="n">
-        <v>6982735</v>
+        <v>6982809</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129130334</v>
+        <v>129131950</v>
       </c>
       <c r="B3" t="n">
-        <v>97555</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538004</v>
+        <v>537923</v>
       </c>
       <c r="R3" t="n">
-        <v>6982735</v>
+        <v>6982809</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129131950</v>
+        <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>97555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537923</v>
+        <v>538004</v>
       </c>
       <c r="R4" t="n">
-        <v>6982809</v>
+        <v>6982735</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129131950</v>
+        <v>129130334</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>97589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537923</v>
+        <v>538004</v>
       </c>
       <c r="R3" t="n">
-        <v>6982809</v>
+        <v>6982735</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129130334</v>
+        <v>129131950</v>
       </c>
       <c r="B4" t="n">
-        <v>97587</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538004</v>
+        <v>537923</v>
       </c>
       <c r="R4" t="n">
-        <v>6982735</v>
+        <v>6982809</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129130334</v>
+        <v>129131950</v>
       </c>
       <c r="B3" t="n">
-        <v>97589</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538004</v>
+        <v>537923</v>
       </c>
       <c r="R3" t="n">
-        <v>6982735</v>
+        <v>6982809</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129131950</v>
+        <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>97593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537923</v>
+        <v>538004</v>
       </c>
       <c r="R4" t="n">
-        <v>6982809</v>
+        <v>6982735</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129131950</v>
+        <v>129130334</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>97604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537923</v>
+        <v>538004</v>
       </c>
       <c r="R3" t="n">
-        <v>6982809</v>
+        <v>6982735</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129130334</v>
+        <v>129131950</v>
       </c>
       <c r="B4" t="n">
-        <v>97604</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538004</v>
+        <v>537923</v>
       </c>
       <c r="R4" t="n">
-        <v>6982735</v>
+        <v>6982809</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129130334</v>
+        <v>129131950</v>
       </c>
       <c r="B3" t="n">
-        <v>97604</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538004</v>
+        <v>537923</v>
       </c>
       <c r="R3" t="n">
-        <v>6982735</v>
+        <v>6982809</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129131950</v>
+        <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>97604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537923</v>
+        <v>538004</v>
       </c>
       <c r="R4" t="n">
-        <v>6982809</v>
+        <v>6982735</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129130282</v>
       </c>
       <c r="B2" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129131950</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129130282</v>
+        <v>129131950</v>
       </c>
       <c r="B2" t="n">
-        <v>57834</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537999</v>
+        <v>537923</v>
       </c>
       <c r="R2" t="n">
-        <v>6982717</v>
+        <v>6982809</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129131950</v>
+        <v>129130282</v>
       </c>
       <c r="B3" t="n">
-        <v>57890</v>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Långmyran, Långmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537923</v>
+        <v>537999</v>
       </c>
       <c r="R3" t="n">
-        <v>6982809</v>
+        <v>6982717</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>129130334</v>
       </c>
       <c r="B4" t="n">
-        <v>97633</v>
+        <v>97989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20070-2022 artfynd.xlsx
+++ b/artfynd/A 20070-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129131950</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130282</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129130334</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>